--- a/output/audit_cuneo.xlsx
+++ b/output/audit_cuneo.xlsx
@@ -535,9 +535,17 @@
           <t>304</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>controllo: OCR e lettura visiva concordi</t>
@@ -576,9 +584,17 @@
           <t>2.905</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -617,9 +633,17 @@
           <t>296,67</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>controllo: OCR e lettura visiva concordi</t>
@@ -658,9 +682,17 @@
           <t>1.510,62</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>controllo: OCR e lettura visiva concordi</t>
@@ -699,9 +731,17 @@
           <t>118,98</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -740,9 +780,17 @@
           <t>405</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>controllo: OCR e lettura visiva concordi</t>
@@ -781,9 +829,17 @@
           <t>562,58</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -822,9 +878,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -863,9 +927,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>controllo: OCR e lettura visiva concordi</t>
@@ -904,9 +976,17 @@
           <t>699,03</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -945,9 +1025,17 @@
           <t>104,49</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -986,9 +1074,17 @@
           <t>164</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>controllo: OCR e lettura visiva concordi</t>
@@ -1027,9 +1123,17 @@
           <t>16</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -1068,9 +1172,17 @@
           <t>52</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -1109,9 +1221,17 @@
           <t>8,86</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -1150,9 +1270,17 @@
           <t>74</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -1191,9 +1319,17 @@
           <t>58,48</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -1232,9 +1368,17 @@
           <t>305,96</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -1273,9 +1417,17 @@
           <t>257</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -1314,9 +1466,17 @@
           <t>1.165,60</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -1355,9 +1515,17 @@
           <t>880,84</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -1396,9 +1564,17 @@
           <t>172</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -1437,9 +1613,17 @@
           <t>152</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -1478,9 +1662,17 @@
           <t>80,00</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -1519,9 +1711,17 @@
           <t>463</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -1560,9 +1760,17 @@
           <t>339</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -1601,9 +1809,17 @@
           <t>298</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -1642,9 +1858,17 @@
           <t>813,76</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -1683,9 +1907,17 @@
           <t>2</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -1724,9 +1956,17 @@
           <t>371</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -1765,9 +2005,17 @@
           <t>2</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>controllo: OCR e lettura visiva concordi</t>
@@ -1806,9 +2054,17 @@
           <t>293</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -1847,9 +2103,17 @@
           <t>345</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>OCR aveva letto un valore diverso</t>
@@ -1888,9 +2152,17 @@
           <t>1.604,70</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
       <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>controllo manuale sul PDF, 2026-10-02</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>controllo: OCR e lettura visiva concordi</t>
@@ -1926,9 +2198,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1964,9 +2234,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -2002,9 +2270,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
